--- a/data/xlsx/pksf--bakery-and-pastry-production.xlsx
+++ b/data/xlsx/pksf--bakery-and-pastry-production.xlsx
@@ -647,7 +647,9 @@
       <c r="C16" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D16" s="9" t="n"/>
+      <c r="D16" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E16" s="9" t="n">
         <v>5</v>
       </c>
@@ -669,7 +671,9 @@
       <c r="C17" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D17" s="9" t="n"/>
+      <c r="D17" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E17" s="9" t="n">
         <v>5</v>
       </c>
@@ -691,7 +695,9 @@
       <c r="C18" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D18" s="9" t="n"/>
+      <c r="D18" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E18" s="9" t="n">
         <v>9</v>
       </c>
@@ -713,7 +719,9 @@
       <c r="C19" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D19" s="9" t="n"/>
+      <c r="D19" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E19" s="9" t="n">
         <v>9</v>
       </c>
@@ -735,7 +743,9 @@
       <c r="C20" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D20" s="9" t="n"/>
+      <c r="D20" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E20" s="9" t="n">
         <v>9</v>
       </c>
@@ -757,7 +767,9 @@
       <c r="C21" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D21" s="9" t="n"/>
+      <c r="D21" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E21" s="9" t="n">
         <v>6</v>
       </c>
@@ -779,7 +791,9 @@
       <c r="C22" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D22" s="9" t="n"/>
+      <c r="D22" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E22" s="9" t="n">
         <v>5</v>
       </c>
@@ -801,7 +815,9 @@
       <c r="C23" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D23" s="9" t="n"/>
+      <c r="D23" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E23" s="9" t="n">
         <v>7</v>
       </c>
@@ -823,7 +839,9 @@
       <c r="C24" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D24" s="9" t="n"/>
+      <c r="D24" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E24" s="9" t="n">
         <v>6</v>
       </c>
@@ -845,7 +863,9 @@
       <c r="C25" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="D25" s="9" t="n"/>
+      <c r="D25" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E25" s="9" t="n">
         <v>6</v>
       </c>
@@ -867,7 +887,9 @@
       <c r="C26" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="D26" s="9" t="n"/>
+      <c r="D26" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E26" s="9" t="n">
         <v>4</v>
       </c>
@@ -889,7 +911,9 @@
       <c r="C27" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D27" s="9" t="n"/>
+      <c r="D27" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E27" s="9" t="n">
         <v>8</v>
       </c>
@@ -911,7 +935,9 @@
       <c r="C28" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D28" s="9" t="n"/>
+      <c r="D28" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E28" s="9" t="n">
         <v>8</v>
       </c>
@@ -933,7 +959,9 @@
       <c r="C29" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D29" s="9" t="n"/>
+      <c r="D29" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E29" s="9" t="n">
         <v>7</v>
       </c>
@@ -955,7 +983,9 @@
       <c r="C30" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D30" s="9" t="n"/>
+      <c r="D30" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E30" s="9" t="n">
         <v>7</v>
       </c>
@@ -977,7 +1007,9 @@
       <c r="C31" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D31" s="9" t="n"/>
+      <c r="D31" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E31" s="9" t="n">
         <v>6</v>
       </c>
@@ -999,7 +1031,9 @@
       <c r="C32" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D32" s="9" t="n"/>
+      <c r="D32" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E32" s="9" t="n">
         <v>5</v>
       </c>
@@ -1021,7 +1055,9 @@
       <c r="C33" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D33" s="9" t="n"/>
+      <c r="D33" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E33" s="9" t="n">
         <v>5</v>
       </c>
@@ -1043,7 +1079,9 @@
       <c r="C34" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D34" s="9" t="n"/>
+      <c r="D34" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E34" s="9" t="n">
         <v>5</v>
       </c>
@@ -1065,7 +1103,9 @@
       <c r="C35" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="D35" s="9" t="n"/>
+      <c r="D35" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E35" s="9" t="n">
         <v>4</v>
       </c>
@@ -1087,7 +1127,9 @@
       <c r="C36" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="D36" s="9" t="n"/>
+      <c r="D36" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E36" s="9" t="n">
         <v>4</v>
       </c>
@@ -1109,7 +1151,9 @@
       <c r="C37" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D37" s="9" t="n"/>
+      <c r="D37" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E37" s="9" t="n">
         <v>4</v>
       </c>
@@ -1131,7 +1175,9 @@
       <c r="C38" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="D38" s="9" t="n"/>
+      <c r="D38" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E38" s="9" t="n">
         <v>3</v>
       </c>

--- a/data/xlsx/pksf--bakery-and-pastry-production.xlsx
+++ b/data/xlsx/pksf--bakery-and-pastry-production.xlsx
@@ -99,7 +99,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="bottom"/>
@@ -132,6 +132,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -636,7 +642,7 @@
       </c>
     </row>
     <row r="16" ht="14.15" customHeight="1">
-      <c r="A16" s="7" t="n">
+      <c r="A16" s="14" t="n">
         <v>1</v>
       </c>
       <c r="B16" s="8" t="inlineStr">
@@ -660,7 +666,7 @@
       <c r="G16" s="9" t="n"/>
     </row>
     <row r="17" ht="14.15" customHeight="1">
-      <c r="A17" s="7" t="n">
+      <c r="A17" s="14" t="n">
         <v>2</v>
       </c>
       <c r="B17" s="8" t="inlineStr">
@@ -684,7 +690,7 @@
       <c r="G17" s="9" t="n"/>
     </row>
     <row r="18" ht="14.15" customHeight="1">
-      <c r="A18" s="7" t="n">
+      <c r="A18" s="14" t="n">
         <v>3</v>
       </c>
       <c r="B18" s="8" t="inlineStr">
@@ -699,7 +705,7 @@
         <v>0</v>
       </c>
       <c r="E18" s="9" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F18" s="9">
         <f>IFERROR(MIN(C18,D18)*E18/C18,0)</f>
@@ -708,7 +714,7 @@
       <c r="G18" s="9" t="n"/>
     </row>
     <row r="19" ht="14.15" customHeight="1">
-      <c r="A19" s="7" t="n">
+      <c r="A19" s="14" t="n">
         <v>4</v>
       </c>
       <c r="B19" s="8" t="inlineStr">
@@ -732,7 +738,7 @@
       <c r="G19" s="9" t="n"/>
     </row>
     <row r="20" ht="14.15" customHeight="1">
-      <c r="A20" s="7" t="n">
+      <c r="A20" s="14" t="n">
         <v>5</v>
       </c>
       <c r="B20" s="8" t="inlineStr">
@@ -756,7 +762,7 @@
       <c r="G20" s="9" t="n"/>
     </row>
     <row r="21" ht="14.15" customHeight="1">
-      <c r="A21" s="7" t="n">
+      <c r="A21" s="14" t="n">
         <v>6</v>
       </c>
       <c r="B21" s="8" t="inlineStr">
@@ -771,7 +777,7 @@
         <v>0</v>
       </c>
       <c r="E21" s="9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F21" s="9">
         <f>IFERROR(MIN(C21,D21)*E21/C21,0)</f>
@@ -780,7 +786,7 @@
       <c r="G21" s="9" t="n"/>
     </row>
     <row r="22" ht="14.15" customHeight="1">
-      <c r="A22" s="7" t="n">
+      <c r="A22" s="14" t="n">
         <v>7</v>
       </c>
       <c r="B22" s="8" t="inlineStr">
@@ -795,7 +801,7 @@
         <v>0</v>
       </c>
       <c r="E22" s="9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F22" s="9">
         <f>IFERROR(MIN(C22,D22)*E22/C22,0)</f>
@@ -804,7 +810,7 @@
       <c r="G22" s="9" t="n"/>
     </row>
     <row r="23" ht="14.15" customHeight="1">
-      <c r="A23" s="7" t="n">
+      <c r="A23" s="14" t="n">
         <v>8</v>
       </c>
       <c r="B23" s="8" t="inlineStr">
@@ -828,7 +834,7 @@
       <c r="G23" s="9" t="n"/>
     </row>
     <row r="24" ht="14.15" customHeight="1">
-      <c r="A24" s="7" t="n">
+      <c r="A24" s="14" t="n">
         <v>9</v>
       </c>
       <c r="B24" s="8" t="inlineStr">
@@ -852,7 +858,7 @@
       <c r="G24" s="9" t="n"/>
     </row>
     <row r="25" ht="14.15" customHeight="1">
-      <c r="A25" s="7" t="n">
+      <c r="A25" s="14" t="n">
         <v>10</v>
       </c>
       <c r="B25" s="8" t="inlineStr">
@@ -876,7 +882,7 @@
       <c r="G25" s="9" t="n"/>
     </row>
     <row r="26" ht="14.15" customHeight="1">
-      <c r="A26" s="7" t="n">
+      <c r="A26" s="14" t="n">
         <v>11</v>
       </c>
       <c r="B26" s="8" t="inlineStr">
@@ -891,7 +897,7 @@
         <v>0</v>
       </c>
       <c r="E26" s="9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F26" s="9">
         <f>IFERROR(MIN(C26,D26)*E26/C26,0)</f>
@@ -900,7 +906,7 @@
       <c r="G26" s="9" t="n"/>
     </row>
     <row r="27" ht="14.15" customHeight="1">
-      <c r="A27" s="7" t="n">
+      <c r="A27" s="14" t="n">
         <v>12</v>
       </c>
       <c r="B27" s="8" t="inlineStr">
@@ -915,7 +921,7 @@
         <v>0</v>
       </c>
       <c r="E27" s="9" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F27" s="9">
         <f>IFERROR(MIN(C27,D27)*E27/C27,0)</f>
@@ -924,7 +930,7 @@
       <c r="G27" s="9" t="n"/>
     </row>
     <row r="28" ht="14.15" customHeight="1">
-      <c r="A28" s="7" t="n">
+      <c r="A28" s="14" t="n">
         <v>13</v>
       </c>
       <c r="B28" s="8" t="inlineStr">
@@ -948,7 +954,7 @@
       <c r="G28" s="9" t="n"/>
     </row>
     <row r="29" ht="14.15" customHeight="1">
-      <c r="A29" s="7" t="n">
+      <c r="A29" s="14" t="n">
         <v>14</v>
       </c>
       <c r="B29" s="8" t="inlineStr">
@@ -963,7 +969,7 @@
         <v>0</v>
       </c>
       <c r="E29" s="9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F29" s="9">
         <f>IFERROR(MIN(C29,D29)*E29/C29,0)</f>
@@ -972,7 +978,7 @@
       <c r="G29" s="9" t="n"/>
     </row>
     <row r="30" ht="14.15" customHeight="1">
-      <c r="A30" s="7" t="n">
+      <c r="A30" s="14" t="n">
         <v>15</v>
       </c>
       <c r="B30" s="8" t="inlineStr">
@@ -996,7 +1002,7 @@
       <c r="G30" s="9" t="n"/>
     </row>
     <row r="31" ht="14.15" customHeight="1">
-      <c r="A31" s="7" t="n">
+      <c r="A31" s="14" t="n">
         <v>16</v>
       </c>
       <c r="B31" s="8" t="inlineStr">
@@ -1020,7 +1026,7 @@
       <c r="G31" s="9" t="n"/>
     </row>
     <row r="32" ht="14.15" customHeight="1">
-      <c r="A32" s="7" t="n">
+      <c r="A32" s="14" t="n">
         <v>17</v>
       </c>
       <c r="B32" s="8" t="inlineStr">
@@ -1035,7 +1041,7 @@
         <v>0</v>
       </c>
       <c r="E32" s="9" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F32" s="9">
         <f>IFERROR(MIN(C32,D32)*E32/C32,0)</f>
@@ -1044,7 +1050,7 @@
       <c r="G32" s="9" t="n"/>
     </row>
     <row r="33" ht="14.15" customHeight="1">
-      <c r="A33" s="7" t="n">
+      <c r="A33" s="14" t="n">
         <v>18</v>
       </c>
       <c r="B33" s="8" t="inlineStr">
@@ -1059,7 +1065,7 @@
         <v>0</v>
       </c>
       <c r="E33" s="9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F33" s="9">
         <f>IFERROR(MIN(C33,D33)*E33/C33,0)</f>
@@ -1068,7 +1074,7 @@
       <c r="G33" s="9" t="n"/>
     </row>
     <row r="34" ht="14.15" customHeight="1">
-      <c r="A34" s="7" t="n">
+      <c r="A34" s="14" t="n">
         <v>19</v>
       </c>
       <c r="B34" s="8" t="inlineStr">
@@ -1092,7 +1098,7 @@
       <c r="G34" s="9" t="n"/>
     </row>
     <row r="35" ht="14.15" customHeight="1">
-      <c r="A35" s="7" t="n">
+      <c r="A35" s="14" t="n">
         <v>20</v>
       </c>
       <c r="B35" s="8" t="inlineStr">
@@ -1116,7 +1122,7 @@
       <c r="G35" s="9" t="n"/>
     </row>
     <row r="36" ht="14.15" customHeight="1">
-      <c r="A36" s="7" t="n">
+      <c r="A36" s="14" t="n">
         <v>21</v>
       </c>
       <c r="B36" s="8" t="inlineStr">
@@ -1140,7 +1146,7 @@
       <c r="G36" s="9" t="n"/>
     </row>
     <row r="37" ht="14.15" customHeight="1">
-      <c r="A37" s="7" t="n">
+      <c r="A37" s="14" t="n">
         <v>22</v>
       </c>
       <c r="B37" s="8" t="inlineStr">
@@ -1164,7 +1170,7 @@
       <c r="G37" s="9" t="n"/>
     </row>
     <row r="38" ht="14.15" customHeight="1">
-      <c r="A38" s="7" t="n">
+      <c r="A38" s="14" t="n">
         <v>23</v>
       </c>
       <c r="B38" s="8" t="inlineStr">
@@ -1188,7 +1194,7 @@
       <c r="G38" s="9" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" s="10" t="inlineStr">
+      <c r="A39" s="15" t="inlineStr">
         <is>
           <t>Sum</t>
         </is>
@@ -1196,18 +1202,18 @@
       <c r="B39" s="11" t="n"/>
       <c r="C39" s="11" t="n"/>
       <c r="D39" s="12" t="n"/>
-      <c r="E39" s="10">
+      <c r="E39" s="15">
         <f>SUM(E16:E38)</f>
         <v/>
       </c>
-      <c r="F39" s="10">
+      <c r="F39" s="15">
         <f>SUM(F16:F38)</f>
         <v/>
       </c>
       <c r="G39" s="13" t="n"/>
     </row>
     <row r="40">
-      <c r="A40" s="10" t="inlineStr">
+      <c r="A40" s="15" t="inlineStr">
         <is>
           <t>Score out of 100</t>
         </is>
@@ -1216,7 +1222,7 @@
       <c r="C40" s="11" t="n"/>
       <c r="D40" s="11" t="n"/>
       <c r="E40" s="12" t="n"/>
-      <c r="F40" s="10">
+      <c r="F40" s="15">
         <f>F39/E39*100</f>
         <v/>
       </c>
@@ -1224,7 +1230,7 @@
     </row>
     <row r="41" ht="9.75" customHeight="1"/>
     <row r="42">
-      <c r="A42" s="10" t="inlineStr">
+      <c r="A42" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">Total achieved points out of 30  </t>
         </is>
@@ -1233,11 +1239,11 @@
       <c r="C42" s="11" t="n"/>
       <c r="D42" s="11" t="n"/>
       <c r="E42" s="12" t="n"/>
-      <c r="F42" s="10">
+      <c r="F42" s="15">
         <f>F40*30/100</f>
         <v/>
       </c>
-      <c r="G42" s="10" t="inlineStr">
+      <c r="G42" s="15" t="inlineStr">
         <is>
           <t>Points</t>
         </is>
